--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HIZLI_BASLANGIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GIRDI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="VARSAYIMLAR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KURALLAR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MOTOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FINANSMAN" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SENARYO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PANO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="KARAR" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="VAKALAR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="KANIT_RAPORU" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="KONTROLLER" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ORNEK_VERI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="LISTELER" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="AYARLAR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="KILAVUZ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -90,9 +93,9 @@
     <definedName name="ListeProjeTipi">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
     <definedName name="gyf_capexOpex">FINANSMAN!$B$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'KANIT_RAPORU'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,12 +103,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -238,8 +243,117 @@
       <color rgb="00B3261E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -276,8 +390,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -286,11 +418,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -507,6 +653,49 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,13 +832,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -673,7 +862,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -725,13 +914,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -755,7 +944,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -807,13 +996,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -837,7 +1026,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -889,13 +1078,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -918,14 +1107,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -977,13 +1166,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1007,7 +1196,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1059,13 +1248,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1089,7 +1278,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1141,13 +1330,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1171,7 +1360,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1223,13 +1412,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1253,7 +1442,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2495,7 +2684,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2510,9 +2699,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2522,7 +2711,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2537,9 +2726,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2559,9 +2748,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2581,9 +2770,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2593,7 +2782,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2608,9 +2797,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2620,7 +2809,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2635,9 +2824,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2647,7 +2836,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2662,9 +2851,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2674,7 +2863,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2689,9 +2878,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3063,146 +3252,1496 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2742"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="B2" s="71" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — GES YATIRIM FIZIBILITE YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Çatı veya saha GES kapasitesi, tüketim eşleştirme, CAPEX/OPEX ve tarife girdilerini işleyin; NPV/IRR aralığı ile YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+      <c r="B4" s="72" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="73" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="73" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="74" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Tüketim eşleştirmeli gelir: öz tüketim tasarrufu + şebeke satış</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• CAPEX / OPEX ayrımı + yıllık degradasyonlu nakit akışı</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="76" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="77" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Öz kaynak / kredi finansman senaryosu (F01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• NPV / IRR aralık + tornado; kötümser YATIRIM YAPMA yolu (F04–F05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Varsayım kaynak+güven ve KANIT_RAPORU (banka/yatırımcı)</t>
+      <c r="B9" s="78" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="80" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="82" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="82" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="82" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="82" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="82" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="82" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="82" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="82" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Tesis sahibi / mühendis — kapasite ve tüketim eşleştirmesini girmek</t>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="84" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="84" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="85">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="86">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="84" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• Yatırımcı / CFO — NPV/IRR ile yatırım kararı vermek</t>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="84" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="84" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="85">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="86">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="84" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Banka kredi komitesi — imzalı fizibilite kanıtını dosyalamak</t>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="84" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="84" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="85">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="86">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="84" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="84" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="84" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="85">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="86">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="84" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="84" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="84" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="85">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="86">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="84" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: GYF-PRO</t>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="84" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="84" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="85">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="86">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="84" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="87" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="88" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
-    <mergeCell ref="A8:AD8"/>
-    <mergeCell ref="A7:AD7"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A11:AD11"/>
-    <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A19:P19"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C65911"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FINANSMAN — GES Yatırım Fizibilite Simülatörü</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Pay</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Tutar [₺]</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>Faiz / maliyet</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>NPV etkisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>OZ_KAYNAK</t>
+        </is>
+      </c>
+      <c r="B6" s="45">
+        <f>GIRDI!B22</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>IFERROR(gyf_capexToplam*B6,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="45">
+        <f>IFERROR(GIRDI!B22*gyf_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>IFERROR(MOTOR!G37,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>KREDI</t>
+        </is>
+      </c>
+      <c r="B7" s="45">
+        <f>gyf_bazCarpan-GIRDI!B22</f>
+        <v/>
+      </c>
+      <c r="C7" s="19">
+        <f>IFERROR(gyf_capexToplam*B7,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="45">
+        <f>GIRDI!B21</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
+        <f>IFERROR(MOTOR!G37-C7*D7*GIRDI!B20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX / YATIRIM toplam</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>IFERROR(gyf_capexToplam,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>OPEX / ISLETME yıllık</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>IFERROR(gyf_opexYillik,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Finansman karşılaştırma</t>
+        </is>
+      </c>
+      <c r="B11" s="37">
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"OZ_KAYNAK NPV ",TEXT(E6,"₺ #,##0")," · KREDI NPV ",TEXT(E7,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX OPEX özet</t>
+        </is>
+      </c>
+      <c r="B12" s="37">
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"CAPEX ",TEXT(B9,"₺ #,##0")," · OPEX ",TEXT(B10,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>FinansDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>OZ_KAYNAK</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>KREDI</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="n">
+        <v>720000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="3">
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:E7">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SENARYO — GES Yatırım Fizibilite Simülatörü</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Senaryo ve duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Çarpan</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Yıllık gelir</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>NpvDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="B6" s="45">
+        <f>IFERROR(gyf_senaryoIyi+N(GIRDI!B10)*gyf_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>IFERROR(MOTOR!G46,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>IFERROR(MOTOR!G48,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="47">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(D6&lt;0,"YATIRIM YAPMA","YATIRIM YAPILIR"))</f>
+        <v/>
+      </c>
+      <c r="G6" s="52" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="B7" s="45">
+        <f>IFERROR(gyf_bazCarpan+N(GIRDI!B10)*gyf_sifirCarpan,1)</f>
+        <v/>
+      </c>
+      <c r="C7" s="19">
+        <f>IFERROR(gyf_yillikGelir,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="19">
+        <f>IFERROR(gyf_npv,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="47">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(gyf_kararMetni,"-"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="52" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="B8" s="45">
+        <f>IFERROR(gyf_senaryoKotu+N(GIRDI!B10)*gyf_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="19">
+        <f>IFERROR(MOTOR!G47,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="19">
+        <f>IFERROR(MOTOR!G49,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(MOTOR!G50,"YATIRIM YAPMA"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="52" t="n">
+        <v>-180000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo NPV bant (iyimser−kötümser)</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>IFERROR(D6-D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo yorumu</t>
+        </is>
+      </c>
+      <c r="B11" s="37">
+        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser NPV ",TEXT(D6,"₺ #,##0")," · Baz ",TEXT(D7,"₺ #,##0")," · Kötümser ",TEXT(D8,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>Değişken</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>Etki [₺]</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>EtkiDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Tornado tarife etkisi</t>
+        </is>
+      </c>
+      <c r="B15" s="19">
+        <f>IFERROR(MOTOR!G51,0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>IFERROR(IF(B15&gt;=MAX(B15:B19),gyf_siraBir,IF(B15=LARGE(B15:B19,2),gyf_siraIki,IF(B15=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
+        <v/>
+      </c>
+      <c r="E15" s="52" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Tornado üretim etkisi</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>IFERROR(MOTOR!G52,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>IFERROR(IF(B16&gt;=MAX(B15:B19),gyf_siraBir,IF(B16=LARGE(B15:B19,2),gyf_siraIki,IF(B16=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
+        <v/>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tornado CAPEX etkisi</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>IFERROR(MOTOR!G53,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>IFERROR(IF(B17&gt;=MAX(B15:B19),gyf_siraBir,IF(B17=LARGE(B15:B19,2),gyf_siraIki,IF(B17=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
+        <v/>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Tornado OPEX etkisi</t>
+        </is>
+      </c>
+      <c r="B18" s="19">
+        <f>IFERROR(MOTOR!G54,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>IFERROR(IF(B18&gt;=MAX(B15:B19),gyf_siraBir,IF(B18=LARGE(B15:B19,2),gyf_siraIki,IF(B18=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
+        <v/>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Tornado WACC etkisi</t>
+        </is>
+      </c>
+      <c r="B19" s="19">
+        <f>IFERROR(MOTOR!G55,0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>IFERROR(IF(B19&gt;=MAX(B15:B19),gyf_siraBir,IF(B19=LARGE(B15:B19,2),gyf_siraIki,IF(B19=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
+        <v/>
+      </c>
+      <c r="E19" s="52" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık sıra özeti</t>
+        </is>
+      </c>
+      <c r="B21" s="47">
+        <f>IFERROR(CONCATENATE("1)",INDEX(A15:A19,MATCH(gyf_siraBir,C15:C19,0))," 2)",INDEX(A15:A19,MATCH(gyf_siraIki,C15:C19,0))),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık yorumu</t>
+        </is>
+      </c>
+      <c r="B22" s="37">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B15:B19),"₺ #,##0")," — öncelik bu değişkende")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin alt</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>IFERROR(gyf_npv*gyf_tahminAlt,0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="19">
+        <f>IFERROR(gyf_npv,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>IFERROR(gyf_npv*gyf_tahminUst,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin (PERCENTILE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Seri nokta</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>TrendDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="19">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="D28" s="52" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="19">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="D29" s="52" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="19">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="D30" s="52" t="n">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="19">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="D31" s="52" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin P90</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
+        <f>IFERROR(PERCENTILE(B28:B31,gyf_yuzdelikOran),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin yorumu</t>
+        </is>
+      </c>
+      <c r="B33" s="37">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 ",TEXT(B32,"₺ #,##0")," · Alt ",TEXT(B24,"₺ #,##0")," · Üst ",TEXT(D24,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D6:D8">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E8">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>ISNUMBER(SEARCH("YAPMA",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>ISNUMBER(SEARCH("YAPILIR",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:B19">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PANO — GES Yatırım Fizibilite Simülatörü</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>Karar panosu</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Yıllık gelir</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Üretim Y1</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Eşleşme</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Geri ödeme</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Güven</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>İyimser NPV</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>Kötümser NPV</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Tahmin P90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="55">
+        <f>IFERROR(gyf_yillikGelir,0)</f>
+        <v/>
+      </c>
+      <c r="C4" s="55">
+        <f>IFERROR(gyf_capexToplam,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="55">
+        <f>IFERROR(gyf_opexYillik,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="56">
+        <f>IFERROR(MOTOR!G26,0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="56">
+        <f>IFERROR(gyf_tuketimEslesme,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="55">
+        <f>IFERROR(gyf_npv,0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="57">
+        <f>IFERROR(gyf_irr,0)</f>
+        <v/>
+      </c>
+      <c r="I4" s="56">
+        <f>IFERROR(MOTOR!G36,0)</f>
+        <v/>
+      </c>
+      <c r="J4" s="56">
+        <f>IFERROR(MOTOR!G42,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="56">
+        <f>IFERROR(MOTOR!G43,0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="55">
+        <f>IFERROR(MOTOR!G48,0)</f>
+        <v/>
+      </c>
+      <c r="M4" s="55">
+        <f>IFERROR(MOTOR!G49,0)</f>
+        <v/>
+      </c>
+      <c r="N4" s="55">
+        <f>IFERROR(gyf_tahminAralik,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Karar özeti</t>
+        </is>
+      </c>
+      <c r="B6" s="58">
+        <f>gyf_kararMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Gerekçe</t>
+        </is>
+      </c>
+      <c r="B7" s="37">
+        <f>gyf_kararGerekce</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Analitik modüller</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="C10" s="48" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="inlineStr">
+        <is>
+          <t>Yorum</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Yıllık üretim / degradasyon</t>
+        </is>
+      </c>
+      <c r="C11" s="20">
+        <f>IFERROR(MOTOR!G26,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Üretim Y1 ",TEXT(C11,"#,##0")," kWh — degradasyon ",TEXT(GIRDI!B12,"0.0%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Tüketim eşleştirme geliri</t>
+        </is>
+      </c>
+      <c r="C12" s="19">
+        <f>IFERROR(gyf_yillikGelir,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Gelir ",TEXT(C12,"₺ #,##0")," — eşleşme ",TEXT(gyf_tuketimEslesme,"#,##0")," kWh")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Senaryo NPV sapması</t>
+        </is>
+      </c>
+      <c r="C13" s="19">
+        <f>IFERROR(ABS(SENARYO!D6-SENARYO!D8),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser NPV bant ",TEXT(C13,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Duyarlılık / tornado</t>
+        </is>
+      </c>
+      <c r="C14" s="47">
+        <f>IFERROR(gyf_duyarlilikSira,"-")</f>
+        <v/>
+      </c>
+      <c r="D14" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Tornado sıra: ",IFERROR(gyf_yorumDuyarlilik,"-"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Senaryo motoru</t>
+        </is>
+      </c>
+      <c r="C15" s="47">
+        <f>IFERROR(gyf_senaryoKarsilastirma,"-")</f>
+        <v/>
+      </c>
+      <c r="D15" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Senaryo: ",IFERROR(gyf_yorumSenaryo,"-"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>O8</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Veri kalite skoru</t>
+        </is>
+      </c>
+      <c r="C16" s="20">
+        <f>IFERROR(MOTOR!G42,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Güven skoru ",TEXT(C16,"0")," / 100")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin + aralık</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>IFERROR(gyf_tahminAralik,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 tahmin ",TEXT(C17,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>NPV yüzdelik P90</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>IFERROR(SENARYO!B32,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="37">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"PERCENTILE P90 ",TEXT(C18,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX/OPEX özeti</t>
+        </is>
+      </c>
+      <c r="B20" s="37">
+        <f>IFERROR(gyf_capexOpex,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>PanoDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>Gelir</t>
+        </is>
+      </c>
+      <c r="B23" s="52" t="n">
+        <v>393000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="51" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="11">
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A1:AN1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
+      <formula>50</formula>
+      <formula>79</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
+      <formula>40</formula>
+      <formula>69</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
+      <formula>40</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4">
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B3261E"/>
@@ -3446,7 +4985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3763,7 +5302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4021,7 +5560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -4162,7 +5701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -10470,7 +12009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -10560,7 +12099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -12114,7 +13653,253 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="89" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="90" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="90" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="90" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="90" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="90" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="90" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="83" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="93" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="83" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="93" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="92" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="83" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="93" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="83" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="93" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="91" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="92" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="83" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="93" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="83" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="93" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -12241,7 +14026,235 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="89" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="94" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="94" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="91" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="91" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — GES Yatırım Fizibilite Simülatörü</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>GES Yatırım Fizibilite Simülatörü</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Çatı veya saha GES kapasitesi, tüketim eşleştirme, CAPEX/OPEX ve tarife girdilerini işleyin; NPV/IRR aralığı ile YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Tüketim eşleştirmeli gelir: öz tüketim tasarrufu + şebeke satış</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• CAPEX / OPEX ayrımı + yıllık degradasyonlu nakit akışı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Öz kaynak / kredi finansman senaryosu (F01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• NPV / IRR aralık + tornado; kötümser YATIRIM YAPMA yolu (F04–F05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Varsayım kaynak+güven ve KANIT_RAPORU (banka/yatırımcı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Tesis sahibi / mühendis — kapasite ve tüketim eşleştirmesini girmek</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• Yatırımcı / CFO — NPV/IRR ile yatırım kararı vermek</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Banka kredi komitesi — imzalı fizibilite kanıtını dosyalamak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: GYF-PRO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A9:AD9"/>
+    <mergeCell ref="A3:AN3"/>
+    <mergeCell ref="A8:AD8"/>
+    <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A11:AD11"/>
+    <mergeCell ref="A10:AD10"/>
+    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A19:P19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -12339,7 +14352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -19121,7 +21134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -19653,7 +21666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -20076,7 +22089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -22089,1140 +24102,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C65911"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FINANSMAN — GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="48" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>Pay</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>Tutar [₺]</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t>Faiz / maliyet</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t>NPV etkisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="49" t="inlineStr">
-        <is>
-          <t>OZ_KAYNAK</t>
-        </is>
-      </c>
-      <c r="B6" s="45">
-        <f>GIRDI!B22</f>
-        <v/>
-      </c>
-      <c r="C6" s="19">
-        <f>IFERROR(gyf_capexToplam*B6,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="45">
-        <f>IFERROR(GIRDI!B22*gyf_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="19">
-        <f>IFERROR(MOTOR!G37,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>KREDI</t>
-        </is>
-      </c>
-      <c r="B7" s="45">
-        <f>gyf_bazCarpan-GIRDI!B22</f>
-        <v/>
-      </c>
-      <c r="C7" s="19">
-        <f>IFERROR(gyf_capexToplam*B7,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="45">
-        <f>GIRDI!B21</f>
-        <v/>
-      </c>
-      <c r="E7" s="19">
-        <f>IFERROR(MOTOR!G37-C7*D7*GIRDI!B20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>CAPEX / YATIRIM toplam</t>
-        </is>
-      </c>
-      <c r="B9" s="19">
-        <f>IFERROR(gyf_capexToplam,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>OPEX / ISLETME yıllık</t>
-        </is>
-      </c>
-      <c r="B10" s="19">
-        <f>IFERROR(gyf_opexYillik,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Finansman karşılaştırma</t>
-        </is>
-      </c>
-      <c r="B11" s="37">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"OZ_KAYNAK NPV ",TEXT(E6,"₺ #,##0")," · KREDI NPV ",TEXT(E7,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>CAPEX OPEX özet</t>
-        </is>
-      </c>
-      <c r="B12" s="37">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"CAPEX ",TEXT(B9,"₺ #,##0")," · OPEX ",TEXT(B10,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50" t="inlineStr">
-        <is>
-          <t>FinansDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="51" t="inlineStr">
-        <is>
-          <t>OZ_KAYNAK</t>
-        </is>
-      </c>
-      <c r="B14" s="52" t="n">
-        <v>480000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="51" t="inlineStr">
-        <is>
-          <t>KREDI</t>
-        </is>
-      </c>
-      <c r="B15" s="52" t="n">
-        <v>720000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SENARYO — GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Senaryo ve duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="48" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>Çarpan</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>Yıllık gelir</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="G5" s="48" t="inlineStr">
-        <is>
-          <t>NpvDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="B6" s="45">
-        <f>IFERROR(gyf_senaryoIyi+N(GIRDI!B10)*gyf_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C6" s="19">
-        <f>IFERROR(MOTOR!G46,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="19">
-        <f>IFERROR(MOTOR!G48,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="47">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(D6&lt;0,"YATIRIM YAPMA","YATIRIM YAPILIR"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="52" t="n">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="B7" s="45">
-        <f>IFERROR(gyf_bazCarpan+N(GIRDI!B10)*gyf_sifirCarpan,1)</f>
-        <v/>
-      </c>
-      <c r="C7" s="19">
-        <f>IFERROR(gyf_yillikGelir,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="19">
-        <f>IFERROR(gyf_npv,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="47">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(gyf_kararMetni,"-"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="52" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="B8" s="45">
-        <f>IFERROR(gyf_senaryoKotu+N(GIRDI!B10)*gyf_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="19">
-        <f>IFERROR(MOTOR!G47,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="19">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="47">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(MOTOR!G50,"YATIRIM YAPMA"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="52" t="n">
-        <v>-180000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo NPV bant (iyimser−kötümser)</t>
-        </is>
-      </c>
-      <c r="B10" s="19">
-        <f>IFERROR(D6-D8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo yorumu</t>
-        </is>
-      </c>
-      <c r="B11" s="37">
-        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser NPV ",TEXT(D6,"₺ #,##0")," · Baz ",TEXT(D7,"₺ #,##0")," · Kötümser ",TEXT(D8,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="48" t="inlineStr">
-        <is>
-          <t>Değişken</t>
-        </is>
-      </c>
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>Etki [₺]</t>
-        </is>
-      </c>
-      <c r="C14" s="48" t="inlineStr">
-        <is>
-          <t>Sıra</t>
-        </is>
-      </c>
-      <c r="E14" s="48" t="inlineStr">
-        <is>
-          <t>EtkiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Tornado tarife etkisi</t>
-        </is>
-      </c>
-      <c r="B15" s="19">
-        <f>IFERROR(MOTOR!G51,0)</f>
-        <v/>
-      </c>
-      <c r="C15" s="20">
-        <f>IFERROR(IF(B15&gt;=MAX(B15:B19),gyf_siraBir,IF(B15=LARGE(B15:B19,2),gyf_siraIki,IF(B15=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
-        <v/>
-      </c>
-      <c r="E15" s="52" t="n">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Tornado üretim etkisi</t>
-        </is>
-      </c>
-      <c r="B16" s="19">
-        <f>IFERROR(MOTOR!G52,0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="20">
-        <f>IFERROR(IF(B16&gt;=MAX(B15:B19),gyf_siraBir,IF(B16=LARGE(B15:B19,2),gyf_siraIki,IF(B16=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
-        <v/>
-      </c>
-      <c r="E16" s="52" t="n">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Tornado CAPEX etkisi</t>
-        </is>
-      </c>
-      <c r="B17" s="19">
-        <f>IFERROR(MOTOR!G53,0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="20">
-        <f>IFERROR(IF(B17&gt;=MAX(B15:B19),gyf_siraBir,IF(B17=LARGE(B15:B19,2),gyf_siraIki,IF(B17=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
-        <v/>
-      </c>
-      <c r="E17" s="52" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Tornado OPEX etkisi</t>
-        </is>
-      </c>
-      <c r="B18" s="19">
-        <f>IFERROR(MOTOR!G54,0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="20">
-        <f>IFERROR(IF(B18&gt;=MAX(B15:B19),gyf_siraBir,IF(B18=LARGE(B15:B19,2),gyf_siraIki,IF(B18=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
-        <v/>
-      </c>
-      <c r="E18" s="52" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Tornado WACC etkisi</t>
-        </is>
-      </c>
-      <c r="B19" s="19">
-        <f>IFERROR(MOTOR!G55,0)</f>
-        <v/>
-      </c>
-      <c r="C19" s="20">
-        <f>IFERROR(IF(B19&gt;=MAX(B15:B19),gyf_siraBir,IF(B19=LARGE(B15:B19,2),gyf_siraIki,IF(B19=LARGE(B15:B19,3),gyf_siraUc,4))),4)</f>
-        <v/>
-      </c>
-      <c r="E19" s="52" t="n">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık sıra özeti</t>
-        </is>
-      </c>
-      <c r="B21" s="47">
-        <f>IFERROR(CONCATENATE("1)",INDEX(A15:A19,MATCH(gyf_siraBir,C15:C19,0))," 2)",INDEX(A15:A19,MATCH(gyf_siraIki,C15:C19,0))),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık yorumu</t>
-        </is>
-      </c>
-      <c r="B22" s="37">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B15:B19),"₺ #,##0")," — öncelik bu değişkende")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin alt</t>
-        </is>
-      </c>
-      <c r="B24" s="19">
-        <f>IFERROR(gyf_npv*gyf_tahminAlt,0)</f>
-        <v/>
-      </c>
-      <c r="C24" s="19">
-        <f>IFERROR(gyf_npv,0)</f>
-        <v/>
-      </c>
-      <c r="D24" s="19">
-        <f>IFERROR(gyf_npv*gyf_tahminUst,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin (PERCENTILE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Seri nokta</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>TrendDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="19">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="D28" s="52" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="19">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="D29" s="52" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="19">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="D30" s="52" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="19">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="D31" s="52" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin P90</t>
-        </is>
-      </c>
-      <c r="B32" s="19">
-        <f>IFERROR(PERCENTILE(B28:B31,gyf_yuzdelikOran),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin yorumu</t>
-        </is>
-      </c>
-      <c r="B33" s="37">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 ",TEXT(B32,"₺ #,##0")," · Alt ",TEXT(B24,"₺ #,##0")," · Üst ",TEXT(D24,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="B11:H11"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6:D8">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E8">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>ISNUMBER(SEARCH("YAPMA",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="5">
-      <formula>ISNUMBER(SEARCH("YAPILIR",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B19">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="54" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Yıllık gelir</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Üretim Y1</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Eşleşme</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Geri ödeme</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>İyimser NPV</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>Kötümser NPV</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Tahmin P90</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="55">
-        <f>IFERROR(gyf_yillikGelir,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="55">
-        <f>IFERROR(gyf_capexToplam,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="55">
-        <f>IFERROR(gyf_opexYillik,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="56">
-        <f>IFERROR(MOTOR!G26,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="56">
-        <f>IFERROR(gyf_tuketimEslesme,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="55">
-        <f>IFERROR(gyf_npv,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="57">
-        <f>IFERROR(gyf_irr,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="56">
-        <f>IFERROR(MOTOR!G36,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="56">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="56">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="55">
-        <f>IFERROR(MOTOR!G48,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="55">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="55">
-        <f>IFERROR(gyf_tahminAralik,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar özeti</t>
-        </is>
-      </c>
-      <c r="B6" s="58">
-        <f>gyf_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="37">
-        <f>gyf_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="48" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="48" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="48" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Yıllık üretim / degradasyon</t>
-        </is>
-      </c>
-      <c r="C11" s="20">
-        <f>IFERROR(MOTOR!G26,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Üretim Y1 ",TEXT(C11,"#,##0")," kWh — degradasyon ",TEXT(GIRDI!B12,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Tüketim eşleştirme geliri</t>
-        </is>
-      </c>
-      <c r="C12" s="19">
-        <f>IFERROR(gyf_yillikGelir,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Gelir ",TEXT(C12,"₺ #,##0")," — eşleşme ",TEXT(gyf_tuketimEslesme,"#,##0")," kWh")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo NPV sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="19">
-        <f>IFERROR(ABS(SENARYO!D6-SENARYO!D8),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser NPV bant ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="47">
-        <f>IFERROR(gyf_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Tornado sıra: ",IFERROR(gyf_yorumDuyarlilik,"-"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="47">
-        <f>IFERROR(gyf_senaryoKarsilastirma,"-")</f>
-        <v/>
-      </c>
-      <c r="D15" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Senaryo: ",IFERROR(gyf_yorumSenaryo,"-"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C16" s="20">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Güven skoru ",TEXT(C16,"0")," / 100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C17" s="19">
-        <f>IFERROR(gyf_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 tahmin ",TEXT(C17,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>NPV yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C18" s="19">
-        <f>IFERROR(SENARYO!B32,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"PERCENTILE P90 ",TEXT(C18,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>CAPEX/OPEX özeti</t>
-        </is>
-      </c>
-      <c r="B20" s="37">
-        <f>IFERROR(gyf_capexOpex,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="50" t="inlineStr">
-        <is>
-          <t>PanoDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="inlineStr">
-        <is>
-          <t>Gelir</t>
-        </is>
-      </c>
-      <c r="B23" s="52" t="n">
-        <v>393000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="51" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="B24" s="52" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="51" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="B25" s="52" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="11">
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="6">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4">
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -7,26 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="hidden" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -93,9 +92,8 @@
     <definedName name="ListeProjeTipi">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
     <definedName name="gyf_capexOpex">FINANSMAN!$B$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'KANIT_RAPORU'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'KANIT_RAPORU'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,14 +101,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="74">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -352,8 +351,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -408,8 +589,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -432,11 +679,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -696,6 +1032,163 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="64" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1177,88 +1670,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pano Özet</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$23:$A$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$23:$B$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Karar NPV Bandı</a:t>
             </a:r>
           </a:p>
@@ -1329,7 +1740,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1411,7 +1822,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2787,7 +3198,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3600000" cy="2520000"/>
@@ -2814,7 +3225,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3600000" cy="2520000"/>
@@ -2836,33 +3247,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3255,351 +3639,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — GES YATIRIM FIZIBILITE YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="72" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="96" t="inlineStr">
+        <is>
+          <t>GES YATIRIM FIZIBILITE — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="97" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="98" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="99" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="100" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="101" t="n"/>
+      <c r="D5" s="102" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="103" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="101" t="n"/>
+      <c r="G5" s="104" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="100" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="101" t="n"/>
+      <c r="J5" s="105" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="106" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="101" t="n"/>
+      <c r="M5" s="102" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="73" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="73" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="74" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="107" t="n"/>
+      <c r="C6" s="101" t="n"/>
+      <c r="D6" s="101" t="n"/>
+      <c r="E6" s="108" t="n"/>
+      <c r="F6" s="101" t="n"/>
+      <c r="G6" s="101" t="n"/>
+      <c r="H6" s="107" t="n"/>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="101" t="n"/>
+      <c r="K6" s="109" t="n"/>
+      <c r="L6" s="101" t="n"/>
+      <c r="M6" s="101" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="75" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="75" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="76" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="77" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="110" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="101" t="n"/>
+      <c r="D7" s="101" t="n"/>
+      <c r="E7" s="111" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="101" t="n"/>
+      <c r="G7" s="101" t="n"/>
+      <c r="H7" s="110" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="101" t="n"/>
+      <c r="J7" s="101" t="n"/>
+      <c r="K7" s="112" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="101" t="n"/>
+      <c r="M7" s="101" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="107" t="n"/>
+      <c r="C8" s="101" t="n"/>
+      <c r="D8" s="101" t="n"/>
+      <c r="E8" s="108" t="n"/>
+      <c r="F8" s="101" t="n"/>
+      <c r="G8" s="101" t="n"/>
+      <c r="H8" s="107" t="n"/>
+      <c r="I8" s="101" t="n"/>
+      <c r="J8" s="101" t="n"/>
+      <c r="K8" s="109" t="n"/>
+      <c r="L8" s="101" t="n"/>
+      <c r="M8" s="101" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="78" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="79" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="80" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="113" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="101" t="n"/>
+      <c r="D9" s="101" t="n"/>
+      <c r="E9" s="114" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="101" t="n"/>
+      <c r="G9" s="101" t="n"/>
+      <c r="H9" s="113" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="101" t="n"/>
+      <c r="J9" s="101" t="n"/>
+      <c r="K9" s="115" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="101" t="n"/>
+      <c r="M9" s="101" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="116" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="94" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B12" s="93" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="93" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="117" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="82" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="82" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="82" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="82" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="82" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="82" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="82" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="83" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="84" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="84" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="85">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="86">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="84" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="87" t="n">
+      <c r="C14" s="117" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="117" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="117" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="118" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="118" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="118" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="118" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="118" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="93" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="93" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="93" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="93" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="119" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="119" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="120" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="121" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="105" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="93" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="93" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="93" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="93" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="119" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="119" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="120" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="121" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="102" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="93" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="93" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="93" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="93" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="119" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="119" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="120" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="121" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="122" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="93" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="93" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="93" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="119" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="119" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="120" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="121" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="105" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="93" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="93" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="93" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="93" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="123" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="124" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="125" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="126" t="inlineStr"/>
+      <c r="L19" s="127" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="93" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="93" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="84" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="84" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="85">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="86">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="84" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="83" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="84" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="84" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="85">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="86">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="84" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="83" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="84" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="84" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="85">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="86">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="84" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="83" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="84" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="84" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="85">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="86">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="84" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="83" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="84" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="84" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="85">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="86">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="84" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="93" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="93" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="128" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="128" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="129" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="130" t="n"/>
+      <c r="M22" s="130" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="78" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="93" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="131" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="132" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="130" t="n"/>
+      <c r="M23" s="130" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="79" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="93" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="131" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="133" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="134" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="78" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="135" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="136" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="137" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4249,499 +4857,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — GES Yatırım Fizibilite Simülatörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="54" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Yıllık gelir</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Üretim Y1</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Eşleşme</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Geri ödeme</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>İyimser NPV</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>Kötümser NPV</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Tahmin P90</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="55">
-        <f>IFERROR(gyf_yillikGelir,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="55">
-        <f>IFERROR(gyf_capexToplam,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="55">
-        <f>IFERROR(gyf_opexYillik,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="56">
-        <f>IFERROR(MOTOR!G26,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="56">
-        <f>IFERROR(gyf_tuketimEslesme,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="55">
-        <f>IFERROR(gyf_npv,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="57">
-        <f>IFERROR(gyf_irr,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="56">
-        <f>IFERROR(MOTOR!G36,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="56">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="56">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="55">
-        <f>IFERROR(MOTOR!G48,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="55">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="55">
-        <f>IFERROR(gyf_tahminAralik,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar özeti</t>
-        </is>
-      </c>
-      <c r="B6" s="58">
-        <f>gyf_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="37">
-        <f>gyf_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="48" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="48" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="48" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Yıllık üretim / degradasyon</t>
-        </is>
-      </c>
-      <c r="C11" s="20">
-        <f>IFERROR(MOTOR!G26,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Üretim Y1 ",TEXT(C11,"#,##0")," kWh — degradasyon ",TEXT(GIRDI!B12,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Tüketim eşleştirme geliri</t>
-        </is>
-      </c>
-      <c r="C12" s="19">
-        <f>IFERROR(gyf_yillikGelir,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Gelir ",TEXT(C12,"₺ #,##0")," — eşleşme ",TEXT(gyf_tuketimEslesme,"#,##0")," kWh")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo NPV sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="19">
-        <f>IFERROR(ABS(SENARYO!D6-SENARYO!D8),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser NPV bant ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="47">
-        <f>IFERROR(gyf_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Tornado sıra: ",IFERROR(gyf_yorumDuyarlilik,"-"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="47">
-        <f>IFERROR(gyf_senaryoKarsilastirma,"-")</f>
-        <v/>
-      </c>
-      <c r="D15" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Senaryo: ",IFERROR(gyf_yorumSenaryo,"-"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C16" s="20">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Güven skoru ",TEXT(C16,"0")," / 100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C17" s="19">
-        <f>IFERROR(gyf_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 tahmin ",TEXT(C17,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>NPV yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C18" s="19">
-        <f>IFERROR(SENARYO!B32,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="37">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"PERCENTILE P90 ",TEXT(C18,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>CAPEX/OPEX özeti</t>
-        </is>
-      </c>
-      <c r="B20" s="37">
-        <f>IFERROR(gyf_capexOpex,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="50" t="inlineStr">
-        <is>
-          <t>PanoDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="inlineStr">
-        <is>
-          <t>Gelir</t>
-        </is>
-      </c>
-      <c r="B23" s="52" t="n">
-        <v>393000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="51" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="B24" s="52" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="51" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="B25" s="52" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="11">
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="6">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4">
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LGES Yatırım Fizibilite Simülatörü · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B3261E"/>
@@ -4985,7 +5100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -5302,7 +5417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -5560,7 +5675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -5701,7 +5816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -12009,7 +12124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -12099,7 +12214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -13653,253 +13768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="90" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="90" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="90" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="90" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="90" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="90" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="91" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="92" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="83" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="93" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="91" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="92" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="83" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="93" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="91" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="92" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="93" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="91" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="92" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="93" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="91" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="92" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="93" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="91" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="83" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="93" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -14026,87 +13895,797 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="138" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="139" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="140" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="141" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="141" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="141" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="141" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="141" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="141" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="141" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="141" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="142" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="143" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="144" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="145" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="147">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="144" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="148" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="149" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="150" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="151" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="152" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="154">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="151" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="155" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="142" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="143" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="144" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="145" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="147">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="144" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="148" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="149" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="150" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="151" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="152" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="154">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="151" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="156" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="142" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="143" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="144" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="145" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="147">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="144" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="148" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="149" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="150" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="151" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="152" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="154">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="151" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="157" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="142" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="143" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="144" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="145" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="147">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="144" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="148" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="149" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="150" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="151" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="152" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="154">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="151" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="156" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="142" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="143" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="144" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="145" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="147">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="144" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="148" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="149" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="150" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="151" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="152" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="154">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="151" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="156" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="158" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="126" t="n"/>
+      <c r="D17" s="126" t="n"/>
+      <c r="E17" s="159">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="126" t="n"/>
+      <c r="G17" s="126" t="n"/>
+      <c r="H17" s="126" t="n"/>
+      <c r="I17" s="126" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="94" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="160" t="inlineStr">
+        <is>
+          <t>GES YATIRIM FIZIBILITE — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="161" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="162" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="163" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="101" t="n"/>
+      <c r="D6" s="101" t="n"/>
+      <c r="E6" s="101" t="n"/>
+      <c r="F6" s="101" t="n"/>
+      <c r="H6" s="164" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="101" t="n"/>
+      <c r="K6" s="101" t="n"/>
+      <c r="L6" s="101" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="101" t="n"/>
+      <c r="C7" s="101" t="n"/>
+      <c r="D7" s="101" t="n"/>
+      <c r="E7" s="101" t="n"/>
+      <c r="F7" s="101" t="n"/>
+      <c r="H7" s="101" t="n"/>
+      <c r="I7" s="101" t="n"/>
+      <c r="J7" s="101" t="n"/>
+      <c r="K7" s="101" t="n"/>
+      <c r="L7" s="101" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="165" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="101" t="n"/>
+      <c r="D8" s="101" t="n"/>
+      <c r="E8" s="166" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="101" t="n"/>
+      <c r="H8" s="165" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="101" t="n"/>
+      <c r="J8" s="101" t="n"/>
+      <c r="K8" s="167" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="101" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="94" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="165" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="101" t="n"/>
+      <c r="D9" s="101" t="n"/>
+      <c r="E9" s="168" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="101" t="n"/>
+      <c r="H9" s="165" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="101" t="n"/>
+      <c r="J9" s="101" t="n"/>
+      <c r="K9" s="168" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="101" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="165" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="101" t="n"/>
+      <c r="D10" s="101" t="n"/>
+      <c r="E10" s="169" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="101" t="n"/>
+      <c r="H10" s="165" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="101" t="n"/>
+      <c r="J10" s="101" t="n"/>
+      <c r="K10" s="169" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="101" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="165" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="101" t="n"/>
+      <c r="D11" s="101" t="n"/>
+      <c r="E11" s="169" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="101" t="n"/>
+      <c r="H11" s="165" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="101" t="n"/>
+      <c r="J11" s="101" t="n"/>
+      <c r="K11" s="169" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="101" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="101" t="n"/>
+      <c r="C12" s="101" t="n"/>
+      <c r="D12" s="101" t="n"/>
+      <c r="E12" s="101" t="n"/>
+      <c r="F12" s="101" t="n"/>
+      <c r="H12" s="101" t="n"/>
+      <c r="I12" s="101" t="n"/>
+      <c r="J12" s="101" t="n"/>
+      <c r="K12" s="101" t="n"/>
+      <c r="L12" s="101" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="94" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="101" t="n"/>
+      <c r="C13" s="101" t="n"/>
+      <c r="D13" s="101" t="n"/>
+      <c r="E13" s="101" t="n"/>
+      <c r="F13" s="101" t="n"/>
+      <c r="H13" s="101" t="n"/>
+      <c r="I13" s="101" t="n"/>
+      <c r="J13" s="101" t="n"/>
+      <c r="K13" s="101" t="n"/>
+      <c r="L13" s="101" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="170" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="101" t="n"/>
+      <c r="D14" s="101" t="n"/>
+      <c r="E14" s="101" t="n"/>
+      <c r="F14" s="101" t="n"/>
+      <c r="H14" s="171" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="101" t="n"/>
+      <c r="J14" s="101" t="n"/>
+      <c r="K14" s="101" t="n"/>
+      <c r="L14" s="101" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="91" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="91" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="101" t="n"/>
+      <c r="C15" s="101" t="n"/>
+      <c r="D15" s="101" t="n"/>
+      <c r="E15" s="101" t="n"/>
+      <c r="F15" s="101" t="n"/>
+      <c r="H15" s="101" t="n"/>
+      <c r="I15" s="101" t="n"/>
+      <c r="J15" s="101" t="n"/>
+      <c r="K15" s="101" t="n"/>
+      <c r="L15" s="101" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="128" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="128" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="128" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="128" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -107,13 +107,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="88">
     <font>
@@ -1175,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1663,6 +1664,24 @@
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="50" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="54" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="55" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="73" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15712,7 +15731,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -15728,7 +15747,7 @@
     <row r="2">
       <c r="B2" s="96" t="inlineStr">
         <is>
-          <t>GES YATIRIM FIZIBILITE — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ</t>
         </is>
       </c>
       <c r="L2" s="97" t="inlineStr">
@@ -15745,53 +15764,53 @@
     <row r="3">
       <c r="B3" s="99" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: GES yatırımcısı, tesis müdürü, CFO, enerji danışmanı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="100" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>YILLIK TAHMİNİ ÜRETİM GELİRİ</t>
         </is>
       </c>
       <c r="C5" s="101" t="n"/>
       <c r="D5" s="102" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>MWh PROJEKSİYON</t>
         </is>
       </c>
       <c r="E5" s="103" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>İŞLETME VE BAKIM (OPEX)</t>
         </is>
       </c>
       <c r="F5" s="101" t="n"/>
       <c r="G5" s="104" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>YILLIK</t>
         </is>
       </c>
       <c r="H5" s="100" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL GETİRİ</t>
         </is>
       </c>
       <c r="I5" s="101" t="n"/>
       <c r="J5" s="105" t="inlineStr">
         <is>
-          <t>GÜVENLİ</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="K5" s="106" t="inlineStr">
         <is>
-          <t>SİSTEM GÜVEN SKORU</t>
+          <t>PROJE İÇ VERİM ORANI (IRR)</t>
         </is>
       </c>
       <c r="L5" s="101" t="n"/>
       <c r="M5" s="102" t="inlineStr">
         <is>
-          <t>DENETLENDİ</t>
+          <t>IRR: %24.2</t>
         </is>
       </c>
     </row>
@@ -15810,31 +15829,27 @@
       <c r="M6" s="101" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="110" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="197">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="101" t="n"/>
       <c r="D7" s="101" t="n"/>
-      <c r="E7" s="111" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="198">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="101" t="n"/>
       <c r="G7" s="101" t="n"/>
-      <c r="H7" s="110" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="197">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="101" t="n"/>
       <c r="J7" s="101" t="n"/>
-      <c r="K7" s="112" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="112">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="101" t="n"/>
       <c r="M7" s="101" t="n"/>
@@ -15856,28 +15871,28 @@
     <row r="9">
       <c r="B9" s="113" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="101" t="n"/>
       <c r="D9" s="101" t="n"/>
       <c r="E9" s="114" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="101" t="n"/>
       <c r="G9" s="101" t="n"/>
       <c r="H9" s="113" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="101" t="n"/>
       <c r="J9" s="101" t="n"/>
       <c r="K9" s="115" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="101" t="n"/>
@@ -15886,7 +15901,7 @@
     <row r="11">
       <c r="B11" s="94" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="116" t="inlineStr">
@@ -15903,7 +15918,7 @@
     <row r="12">
       <c r="B12" s="93" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="93" t="inlineStr">
@@ -15976,18 +15991,16 @@
       </c>
       <c r="H15" s="119" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="119" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="120" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="199">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="200">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="121" t="inlineStr">
         <is>
@@ -16017,18 +16030,16 @@
       </c>
       <c r="H16" s="119" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="119" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="120" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="199">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="200">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="121" t="inlineStr">
         <is>
@@ -16058,18 +16069,16 @@
       </c>
       <c r="H17" s="119" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="119" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="120" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="199">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="200">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="121" t="inlineStr">
         <is>
@@ -16099,18 +16108,16 @@
       </c>
       <c r="H18" s="119" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="119" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="120" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="199">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="200">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="121" t="inlineStr">
         <is>
@@ -16143,15 +16150,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="124" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="125" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="201">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="202">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="126" t="inlineStr"/>
       <c r="L19" s="127" t="inlineStr">
@@ -16213,7 +16218,7 @@
       </c>
       <c r="K23" s="132" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>AMORTİSMAN VE GERİ DÖNÜŞ</t>
         </is>
       </c>
       <c r="L23" s="130" t="n"/>
@@ -16237,7 +16242,7 @@
       </c>
       <c r="K24" s="133" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Yatırım geri dönüş süresi 4.2 yıl olarak hesaplanmış, şebeke alım garantisi teyit edilmiştir.</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16271,7 @@
       </c>
       <c r="K26" s="137" t="inlineStr">
         <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+          <t>FİZİBİLİTE SENARYOSUNU AÇ &gt;</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24795,7 @@
     <row r="3">
       <c r="B3" s="138" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="139" t="inlineStr">
@@ -24859,10 +24864,10 @@
       </c>
       <c r="D6" s="144" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="145" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="203" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="146" t="n">
@@ -24896,10 +24901,10 @@
       </c>
       <c r="D7" s="151" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="152" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="203" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="153" t="n">
@@ -24933,10 +24938,10 @@
       </c>
       <c r="D8" s="144" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="145" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="203" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="146" t="n">
@@ -24970,10 +24975,10 @@
       </c>
       <c r="D9" s="151" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="152" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="203" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="153" t="n">
@@ -25007,10 +25012,10 @@
       </c>
       <c r="D10" s="144" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="145" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="203" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="146" t="n">
@@ -25044,10 +25049,10 @@
       </c>
       <c r="D11" s="151" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="152" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="203" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="153" t="n">
@@ -25059,7 +25064,7 @@
       </c>
       <c r="H11" s="151" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="157" t="inlineStr">
@@ -25081,10 +25086,10 @@
       </c>
       <c r="D12" s="144" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="145" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="203" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="146" t="n">
@@ -25096,7 +25101,7 @@
       </c>
       <c r="H12" s="144" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="148" t="inlineStr">
@@ -25118,10 +25123,10 @@
       </c>
       <c r="D13" s="151" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="152" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="203" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="153" t="n">
@@ -25155,10 +25160,10 @@
       </c>
       <c r="D14" s="144" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="145" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="203" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="146" t="n">
@@ -25192,10 +25197,10 @@
       </c>
       <c r="D15" s="151" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="152" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="203" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="153" t="n">
@@ -25279,14 +25284,14 @@
     <row r="2">
       <c r="B2" s="160" t="inlineStr">
         <is>
-          <t>GES YATIRIM FIZIBILITE — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="161" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · GES yatırımcısı, tesis müdürü, CFO, enerji danışmanı</t>
         </is>
       </c>
     </row>
@@ -25365,10 +25370,9 @@
       </c>
       <c r="C9" s="101" t="n"/>
       <c r="D9" s="101" t="n"/>
-      <c r="E9" s="168" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="204">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="101" t="n"/>
       <c r="H9" s="165" t="inlineStr">
@@ -25378,10 +25382,9 @@
       </c>
       <c r="I9" s="101" t="n"/>
       <c r="J9" s="101" t="n"/>
-      <c r="K9" s="168" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="204">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="101" t="n"/>
     </row>
@@ -25393,10 +25396,9 @@
       </c>
       <c r="C10" s="101" t="n"/>
       <c r="D10" s="101" t="n"/>
-      <c r="E10" s="169" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="205">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="101" t="n"/>
       <c r="H10" s="165" t="inlineStr">
@@ -25406,10 +25408,9 @@
       </c>
       <c r="I10" s="101" t="n"/>
       <c r="J10" s="101" t="n"/>
-      <c r="K10" s="169" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="205">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="101" t="n"/>
     </row>
@@ -25421,10 +25422,9 @@
       </c>
       <c r="C11" s="101" t="n"/>
       <c r="D11" s="101" t="n"/>
-      <c r="E11" s="169" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="206">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="101" t="n"/>
       <c r="H11" s="165" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -116,7 +116,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="88">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -621,8 +621,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -806,6 +818,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1176,7 +1194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1682,6 +1700,33 @@
     </xf>
     <xf numFmtId="170" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4134,20 +4179,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="173" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="174" t="inlineStr">
         <is>
@@ -4412,6 +4474,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="177" t="inlineStr">
         <is>
@@ -4510,7 +4573,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4527,17 +4590,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KAPAK — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="226" t="inlineStr">
         <is>
           <t>GES Yatırım Fizibilite Simülatörü</t>
         </is>
@@ -4550,6 +4631,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4592,6 +4674,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4620,6 +4703,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4634,6 +4718,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4645,13 +4730,13 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="9">
     <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
     <mergeCell ref="A8:AD8"/>
     <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A11:AD11"/>
     <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4668,17 +4753,34 @@
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="126.5" customWidth="1" min="1" max="1"/>
+    <col width="90.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4686,6 +4788,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4722,6 +4825,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4736,6 +4840,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4750,7 +4855,7 @@
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4767,22 +4872,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="29.5" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>GIRDI — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>GES proje girdileri</t>
         </is>
@@ -5073,6 +5191,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -5117,6 +5236,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
@@ -11397,6 +11517,32 @@
         <v/>
       </c>
     </row>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
     <row r="1031" ht="20" customHeight="1">
       <c r="A1031" s="28" t="inlineStr">
         <is>
@@ -11406,9 +11552,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A1031:AN1031"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B17">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -11548,32 +11695,42 @@
   <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="30.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>VARSAYIMLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Model varsayımları — her satırda kaynak ve güven</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -12026,6 +12183,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="J17" s="10" t="inlineStr">
         <is>
@@ -12052,7 +12210,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H15">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -12093,15 +12251,24 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KURALLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Tarife / teşvik kural tablosu (yıl yan yana)</t>
         </is>
@@ -12114,6 +12281,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -12421,6 +12589,8 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
@@ -12467,9 +12637,9 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F7:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="0 ve üzeri sayı." promptTitle="Kural değeri" prompt="Yıl kolonuna sayısal parametre girin." type="decimal" errorStyle="stop" operator="between">
@@ -12510,17 +12680,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>MOTOR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Hesap zinciri — her adımda kural_id · para_dunyasi=nominal</t>
         </is>
@@ -12533,6 +12715,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -14487,8 +14670,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G70">
@@ -14521,24 +14704,39 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>FINANSMAN — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -14612,6 +14810,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -14686,9 +14885,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E7">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -14713,28 +14912,42 @@
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="39.5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>SENARYO — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Senaryo ve duyarlılık (tornado)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -14845,6 +15058,7 @@
         <v>-180000</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -14867,6 +15081,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -14986,6 +15201,7 @@
         <v>70000</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
@@ -15008,6 +15224,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -15027,6 +15244,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -15118,8 +15336,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B11:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D8">
@@ -15163,15 +15382,32 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KARAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="54" t="inlineStr">
         <is>
@@ -15179,6 +15415,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -15201,6 +15438,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
@@ -15256,6 +15494,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -15267,6 +15506,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -15300,6 +15540,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="50" t="inlineStr">
         <is>
@@ -15340,9 +15581,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -15405,30 +15646,40 @@
   <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>VAKALAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Altın vakalar — beklenen vs hesaplanan</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -15619,6 +15870,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -15641,6 +15894,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="50" t="inlineStr">
         <is>
@@ -15692,7 +15946,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G9">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -15719,22 +15973,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="68.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="19.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="97.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15768,6 +16023,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="100" t="inlineStr">
         <is>
@@ -15898,6 +16154,7 @@
       <c r="L9" s="101" t="n"/>
       <c r="M9" s="101" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="94" t="inlineStr">
         <is>
@@ -15927,6 +16184,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="117" t="inlineStr">
         <is>
@@ -16181,6 +16439,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="128" t="inlineStr">
         <is>
@@ -16269,13 +16528,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="209" t="n"/>
+      <c r="H26" s="209" t="n"/>
+      <c r="I26" s="210" t="n"/>
       <c r="K26" s="137" t="inlineStr">
         <is>
           <t>FİZİBİLİTE SENARYOSUNU AÇ &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="211" t="n"/>
+      <c r="G27" s="212" t="n"/>
+      <c r="H27" s="212" t="n"/>
+      <c r="I27" s="213" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -16296,24 +16563,42 @@
   <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="33.5" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KANIT RAPORU — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="54" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Bankaya / yatırımcıya fizibilite kanıtı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -16358,6 +16643,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -16402,6 +16688,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -16435,6 +16722,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -16468,6 +16756,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
@@ -16492,6 +16781,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
@@ -16505,10 +16795,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B20">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -16555,23 +16846,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="55.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KONTROLLER — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Dosya sağlık kontrolleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -16662,8 +16971,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B11">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -16696,33 +17006,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="18.5" customWidth="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="6" max="6"/>
+    <col width="16.5" customWidth="1" min="7" max="7"/>
+    <col width="15.5" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>ORNEK VERI — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+      <c r="J1" s="208" t="n"/>
+      <c r="K1" s="208" t="n"/>
+      <c r="L1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Örnek senaryolar (CSV ile uyumlu)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -22966,8 +23290,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -23000,28 +23325,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>LISTELER — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Doğrulama listeleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -23076,8 +23418,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23095,29 +23438,39 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>AYARLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Parametreler (tek kaynak) — tarife/teşvik</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -24607,6 +24960,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="J44" s="8" t="inlineStr">
         <is>
@@ -24616,8 +24970,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="2025-2027." promptTitle="Hesap Yılı" prompt="Aktif yılı seçin." type="list" errorStyle="stop">
@@ -24647,17 +25002,34 @@
   <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="164.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KILAVUZ — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -24665,6 +25037,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -24693,6 +25066,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="69" t="inlineStr">
         <is>
@@ -24707,6 +25081,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="70" t="inlineStr">
         <is>
@@ -24714,6 +25089,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -24726,6 +25102,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -24740,6 +25117,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -24755,10 +25133,10 @@
     <mergeCell ref="A8:T8"/>
     <mergeCell ref="A6:T6"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:T7"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24771,18 +25149,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24792,12 +25171,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="138" t="inlineStr">
         <is>
           <t>🔍  GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="214" t="n"/>
+      <c r="D3" s="214" t="n"/>
+      <c r="E3" s="215" t="n"/>
       <c r="G3" s="139" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -24809,6 +25192,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="141" t="inlineStr">
         <is>
@@ -25221,22 +25605,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="158" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="126" t="n"/>
-      <c r="D17" s="126" t="n"/>
       <c r="E17" s="159">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="126" t="n"/>
-      <c r="G17" s="126" t="n"/>
-      <c r="H17" s="126" t="n"/>
-      <c r="I17" s="126" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -25257,7 +25636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25302,25 +25681,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="163" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="101" t="n"/>
-      <c r="D6" s="101" t="n"/>
-      <c r="E6" s="101" t="n"/>
-      <c r="F6" s="101" t="n"/>
+      <c r="C6" s="214" t="n"/>
+      <c r="D6" s="214" t="n"/>
+      <c r="E6" s="214" t="n"/>
+      <c r="F6" s="215" t="n"/>
       <c r="H6" s="164" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="101" t="n"/>
-      <c r="J6" s="101" t="n"/>
-      <c r="K6" s="101" t="n"/>
-      <c r="L6" s="101" t="n"/>
+      <c r="I6" s="214" t="n"/>
+      <c r="J6" s="214" t="n"/>
+      <c r="K6" s="214" t="n"/>
+      <c r="L6" s="215" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="101" t="n"/>
@@ -25471,32 +25851,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="101" t="n"/>
-      <c r="D14" s="101" t="n"/>
-      <c r="E14" s="101" t="n"/>
-      <c r="F14" s="101" t="n"/>
+      <c r="C14" s="216" t="n"/>
+      <c r="D14" s="216" t="n"/>
+      <c r="E14" s="216" t="n"/>
+      <c r="F14" s="217" t="n"/>
       <c r="H14" s="171" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="101" t="n"/>
-      <c r="J14" s="101" t="n"/>
-      <c r="K14" s="101" t="n"/>
-      <c r="L14" s="101" t="n"/>
+      <c r="I14" s="218" t="n"/>
+      <c r="J14" s="218" t="n"/>
+      <c r="K14" s="218" t="n"/>
+      <c r="L14" s="219" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="101" t="n"/>
-      <c r="C15" s="101" t="n"/>
-      <c r="D15" s="101" t="n"/>
-      <c r="E15" s="101" t="n"/>
-      <c r="F15" s="101" t="n"/>
-      <c r="H15" s="101" t="n"/>
-      <c r="I15" s="101" t="n"/>
-      <c r="J15" s="101" t="n"/>
-      <c r="K15" s="101" t="n"/>
-      <c r="L15" s="101" t="n"/>
-    </row>
+      <c r="B15" s="220" t="n"/>
+      <c r="C15" s="221" t="n"/>
+      <c r="D15" s="221" t="n"/>
+      <c r="E15" s="221" t="n"/>
+      <c r="F15" s="222" t="n"/>
+      <c r="H15" s="223" t="n"/>
+      <c r="I15" s="224" t="n"/>
+      <c r="J15" s="224" t="n"/>
+      <c r="K15" s="224" t="n"/>
+      <c r="L15" s="225" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="81" t="inlineStr">
         <is>
@@ -25504,6 +25885,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="128" t="inlineStr">
         <is>
@@ -25578,25 +25960,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="178" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="179" t="inlineStr">
         <is>
@@ -26056,7 +26450,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26069,22 +26463,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="181" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
@@ -26796,7 +27205,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26809,24 +27218,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="187" t="inlineStr">
         <is>
@@ -27469,7 +27891,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27482,24 +27904,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="190" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="191" t="inlineStr">
         <is>
@@ -28014,7 +28449,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28027,23 +28462,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="207" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="208" t="n"/>
+      <c r="D1" s="208" t="n"/>
+      <c r="E1" s="208" t="n"/>
+      <c r="F1" s="208" t="n"/>
+      <c r="G1" s="208" t="n"/>
+      <c r="H1" s="208" t="n"/>
+      <c r="I1" s="208" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -28590,7 +29039,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -4179,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4200,14 +4200,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -4586,7 +4578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4607,14 +4599,6 @@
           <t>KAPAK — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4750,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="126.5" customWidth="1" min="1" max="1"/>
@@ -4771,14 +4755,6 @@
           <t>HIZLI BASLANGIC — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -4889,14 +4865,6 @@
           <t>GIRDI — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11692,7 +11660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.5" customWidth="1" min="1" max="1"/>
@@ -11714,13 +11682,6 @@
           <t>VARSAYIMLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -12235,7 +12196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12257,14 +12218,6 @@
           <t>KURALLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -12670,7 +12623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD64"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12691,14 +12644,6 @@
           <t>MOTOR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13885,7 +13830,7 @@
         </is>
       </c>
       <c r="C41" s="37">
-        <f>IFERROR(IF(G39="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G39="YAPILIR","NPV pozitif ve geri ödeme hedef altında; GES yatırımı uygun.",IF(G39="DIKKAT","Geri ödeme veya NPV dikkat bandında; tarife/üretimi gözden geçirin.","NPV negatif veya geri ödeme aşırı; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G39="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G39="YAPILIR","NPV pozitif AND geri ödeme hedef altında; GES yatırımı uygun.",IF(G39="DIKKAT","Geri ödeme veya NPV dikkat bandında; tarife/üretimi gözden geçirin.","NPV negatif veya geri ödeme aşırı; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
       <c r="D41" s="41" t="inlineStr">
@@ -13904,7 +13849,7 @@
         </is>
       </c>
       <c r="G41" s="47">
-        <f>IFERROR(IF(G39="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G39="YAPILIR","NPV pozitif ve geri ödeme hedef altında; GES yatırımı uygun.",IF(G39="DIKKAT","Geri ödeme veya NPV dikkat bandında; tarife/üretimi gözden geçirin.","NPV negatif veya geri ödeme aşırı; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G39="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G39="YAPILIR","NPV pozitif AND geri ödeme hedef altında; GES yatırımı uygun.",IF(G39="DIKKAT","Geri ödeme veya NPV dikkat bandında; tarife/üretimi gözden geçirin.","NPV negatif veya geri ödeme aşırı; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
     </row>
@@ -14698,7 +14643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -14719,14 +14664,6 @@
           <t>FINANSMAN — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14909,7 +14846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.5" customWidth="1" min="1" max="1"/>
@@ -14930,14 +14867,6 @@
           <t>SENARYO — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15377,7 +15306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15398,14 +15327,6 @@
           <t>KARAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -15643,7 +15564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.5" customWidth="1" min="1" max="1"/>
@@ -15663,13 +15584,6 @@
           <t>VAKALAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15973,7 +15887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16104,7 +16018,7 @@
       <c r="I7" s="101" t="n"/>
       <c r="J7" s="101" t="n"/>
       <c r="K7" s="112">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="101" t="n"/>
@@ -16409,11 +16323,11 @@
         </is>
       </c>
       <c r="I19" s="201">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="202">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="126" t="inlineStr"/>
@@ -16560,7 +16474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.5" customWidth="1" min="1" max="1"/>
@@ -16581,14 +16495,6 @@
           <t>KANIT RAPORU — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16796,10 +16702,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B19:H19"/>
     <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <conditionalFormatting sqref="B20">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -16842,7 +16748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16863,14 +16769,6 @@
           <t>KONTROLLER — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17002,7 +16900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17026,17 +16924,6 @@
           <t>ORNEK VERI — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
-      <c r="J1" s="208" t="n"/>
-      <c r="K1" s="208" t="n"/>
-      <c r="L1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -23325,7 +23212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23346,14 +23233,6 @@
           <t>LISTELER — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -23433,7 +23312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -23454,13 +23333,6 @@
           <t>AYARLAR — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -24999,7 +24871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="164.5" customWidth="1" min="1" max="1"/>
@@ -25020,14 +24892,6 @@
           <t>KILAVUZ — GES Yatırım Fizibilite Simülatörü</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -25135,8 +24999,8 @@
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:T7"/>
+    <mergeCell ref="A11:T11"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A11:T11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25149,7 +25013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25613,7 +25477,7 @@
         </is>
       </c>
       <c r="E17" s="159">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -25636,7 +25500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25803,7 +25667,7 @@
       <c r="C11" s="101" t="n"/>
       <c r="D11" s="101" t="n"/>
       <c r="E11" s="206">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="101" t="n"/>
@@ -25960,7 +25824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25981,14 +25845,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -26463,7 +26319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26484,14 +26340,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -27218,7 +27066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -27239,14 +27087,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -27904,7 +27744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -27925,14 +27765,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -28462,7 +28294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -28483,14 +28315,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="208" t="n"/>
-      <c r="C1" s="208" t="n"/>
-      <c r="D1" s="208" t="n"/>
-      <c r="E1" s="208" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="208" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="208" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-yatirim-fizibilite/GesYatirimFizibilite.xlsx
@@ -116,7 +116,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="125">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -633,8 +633,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -826,8 +1032,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1190,11 +1420,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1727,6 +2299,235 @@
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="93" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="95" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="93" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="68" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="68" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="107" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="108" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="110" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4201,7 +5002,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="174" t="inlineStr">
         <is>
@@ -4466,7 +5266,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="177" t="inlineStr">
         <is>
@@ -4600,7 +5399,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="226" t="inlineStr">
         <is>
@@ -4615,7 +5413,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4658,7 +5455,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4687,7 +5483,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4702,7 +5497,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4756,7 +5550,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4764,7 +5557,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4801,7 +5593,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4816,7 +5607,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4866,7 +5656,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -5159,7 +5948,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -5204,7 +5992,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
@@ -11485,32 +12272,6 @@
         <v/>
       </c>
     </row>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
     <row r="1031" ht="20" customHeight="1">
       <c r="A1031" s="28" t="inlineStr">
         <is>
@@ -11683,7 +12444,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -11691,7 +12451,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -12144,7 +12903,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="J17" s="10" t="inlineStr">
         <is>
@@ -12219,7 +12977,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -12234,7 +12991,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -12542,8 +13298,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
@@ -12645,7 +13399,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -12660,7 +13413,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -14665,7 +15417,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -14673,7 +15424,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -14747,7 +15497,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -14868,7 +15617,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -14876,7 +15624,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -14987,7 +15734,6 @@
         <v>-180000</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -15010,7 +15756,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -15130,7 +15875,6 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
@@ -15153,7 +15897,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -15173,7 +15916,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -15328,7 +16070,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="54" t="inlineStr">
         <is>
@@ -15336,7 +16077,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -15359,7 +16099,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
@@ -15415,7 +16154,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -15427,7 +16165,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -15461,7 +16198,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="50" t="inlineStr">
         <is>
@@ -15585,7 +16321,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -15593,7 +16328,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -15784,8 +16518,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -15808,7 +16540,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="50" t="inlineStr">
         <is>
@@ -15890,554 +16621,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="68.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="97.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="228" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="96" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="229" t="inlineStr">
         <is>
           <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ</t>
         </is>
       </c>
-      <c r="L2" s="97" t="inlineStr">
+      <c r="L2" s="230" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="M2" s="231" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="99" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="232" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: GES yatırımcısı, tesis müdürü, CFO, enerji danışmanı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="100" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="233" t="inlineStr">
         <is>
           <t>YILLIK TAHMİNİ ÜRETİM GELİRİ</t>
         </is>
       </c>
-      <c r="C5" s="101" t="n"/>
-      <c r="D5" s="102" t="inlineStr">
+      <c r="C5" s="234" t="n"/>
+      <c r="D5" s="235" t="inlineStr">
         <is>
           <t>MWh PROJEKSİYON</t>
         </is>
       </c>
-      <c r="E5" s="103" t="inlineStr">
+      <c r="E5" s="236" t="inlineStr">
         <is>
           <t>İŞLETME VE BAKIM (OPEX)</t>
         </is>
       </c>
-      <c r="F5" s="101" t="n"/>
-      <c r="G5" s="104" t="inlineStr">
+      <c r="F5" s="234" t="n"/>
+      <c r="G5" s="237" t="inlineStr">
         <is>
           <t>YILLIK</t>
         </is>
       </c>
-      <c r="H5" s="100" t="inlineStr">
+      <c r="H5" s="238" t="inlineStr">
         <is>
           <t>NET OPERASYONEL GETİRİ</t>
         </is>
       </c>
-      <c r="I5" s="101" t="n"/>
-      <c r="J5" s="105" t="inlineStr">
+      <c r="I5" s="234" t="n"/>
+      <c r="J5" s="239" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="K5" s="106" t="inlineStr">
+      <c r="K5" s="240" t="inlineStr">
         <is>
           <t>PROJE İÇ VERİM ORANI (IRR)</t>
         </is>
       </c>
-      <c r="L5" s="101" t="n"/>
-      <c r="M5" s="102" t="inlineStr">
+      <c r="L5" s="234" t="n"/>
+      <c r="M5" s="241" t="inlineStr">
         <is>
           <t>IRR: %24.2</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="107" t="n"/>
-      <c r="C6" s="101" t="n"/>
-      <c r="D6" s="101" t="n"/>
-      <c r="E6" s="108" t="n"/>
-      <c r="F6" s="101" t="n"/>
-      <c r="G6" s="101" t="n"/>
-      <c r="H6" s="107" t="n"/>
-      <c r="I6" s="101" t="n"/>
-      <c r="J6" s="101" t="n"/>
-      <c r="K6" s="109" t="n"/>
-      <c r="L6" s="101" t="n"/>
-      <c r="M6" s="101" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="197">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="242" t="n"/>
+      <c r="C6" s="243" t="n"/>
+      <c r="D6" s="244" t="n"/>
+      <c r="E6" s="245" t="n"/>
+      <c r="F6" s="243" t="n"/>
+      <c r="G6" s="244" t="n"/>
+      <c r="H6" s="246" t="n"/>
+      <c r="I6" s="243" t="n"/>
+      <c r="J6" s="244" t="n"/>
+      <c r="K6" s="247" t="n"/>
+      <c r="L6" s="243" t="n"/>
+      <c r="M6" s="244" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="248">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="101" t="n"/>
-      <c r="D7" s="101" t="n"/>
-      <c r="E7" s="198">
+      <c r="C7" s="243" t="n"/>
+      <c r="D7" s="244" t="n"/>
+      <c r="E7" s="249">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="101" t="n"/>
-      <c r="G7" s="101" t="n"/>
-      <c r="H7" s="197">
+      <c r="F7" s="243" t="n"/>
+      <c r="G7" s="244" t="n"/>
+      <c r="H7" s="250">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="101" t="n"/>
-      <c r="J7" s="101" t="n"/>
-      <c r="K7" s="112">
+      <c r="I7" s="243" t="n"/>
+      <c r="J7" s="244" t="n"/>
+      <c r="K7" s="251">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="101" t="n"/>
-      <c r="M7" s="101" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="101" t="n"/>
-      <c r="D8" s="101" t="n"/>
-      <c r="E8" s="108" t="n"/>
-      <c r="F8" s="101" t="n"/>
-      <c r="G8" s="101" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="101" t="n"/>
-      <c r="J8" s="101" t="n"/>
-      <c r="K8" s="109" t="n"/>
-      <c r="L8" s="101" t="n"/>
-      <c r="M8" s="101" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="113" t="inlineStr">
+      <c r="L7" s="243" t="n"/>
+      <c r="M7" s="244" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="242" t="n"/>
+      <c r="C8" s="243" t="n"/>
+      <c r="D8" s="244" t="n"/>
+      <c r="E8" s="245" t="n"/>
+      <c r="F8" s="243" t="n"/>
+      <c r="G8" s="244" t="n"/>
+      <c r="H8" s="246" t="n"/>
+      <c r="I8" s="243" t="n"/>
+      <c r="J8" s="244" t="n"/>
+      <c r="K8" s="247" t="n"/>
+      <c r="L8" s="243" t="n"/>
+      <c r="M8" s="244" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="252" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="101" t="n"/>
-      <c r="D9" s="101" t="n"/>
-      <c r="E9" s="114" t="inlineStr">
+      <c r="C9" s="253" t="n"/>
+      <c r="D9" s="254" t="n"/>
+      <c r="E9" s="255" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="101" t="n"/>
-      <c r="G9" s="101" t="n"/>
-      <c r="H9" s="113" t="inlineStr">
+      <c r="F9" s="253" t="n"/>
+      <c r="G9" s="254" t="n"/>
+      <c r="H9" s="256" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="101" t="n"/>
-      <c r="J9" s="101" t="n"/>
-      <c r="K9" s="115" t="inlineStr">
+      <c r="I9" s="253" t="n"/>
+      <c r="J9" s="254" t="n"/>
+      <c r="K9" s="257" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="101" t="n"/>
-      <c r="M9" s="101" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="94" t="inlineStr">
+      <c r="L9" s="253" t="n"/>
+      <c r="M9" s="254" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="258" t="inlineStr">
         <is>
           <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="116" t="inlineStr">
+      <c r="F11" s="259" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="94" t="inlineStr">
+      <c r="H11" s="258" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="93" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="99" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="93" t="inlineStr">
+      <c r="H12" s="99" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="117" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="260" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="117" t="inlineStr">
+      <c r="C14" s="260" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="117" t="inlineStr">
+      <c r="D14" s="260" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="117" t="inlineStr">
+      <c r="E14" s="260" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="118" t="inlineStr">
+      <c r="H14" s="261" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="118" t="inlineStr">
+      <c r="I14" s="262" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="118" t="inlineStr">
+      <c r="J14" s="262" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="118" t="inlineStr">
+      <c r="K14" s="262" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="118" t="inlineStr">
+      <c r="L14" s="262" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="93" t="inlineStr">
+      <c r="M14" s="262" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="263" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="93" t="n">
+      <c r="C15" s="263" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="93" t="n">
+      <c r="D15" s="263" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="93" t="n">
+      <c r="E15" s="263" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="119" t="inlineStr">
+      <c r="H15" s="264" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="199">
+      <c r="I15" s="265">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="200">
+      <c r="J15" s="266">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="121" t="inlineStr">
+      <c r="K15" s="267" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="268" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="93" t="inlineStr">
+      <c r="M15" s="269" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="270" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="93" t="n">
+      <c r="C16" s="270" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="93" t="n">
+      <c r="D16" s="270" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="93" t="n">
+      <c r="E16" s="270" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="119" t="inlineStr">
+      <c r="H16" s="271" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="199">
+      <c r="I16" s="272">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="200">
+      <c r="J16" s="273">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="121" t="inlineStr">
+      <c r="K16" s="274" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="102" t="inlineStr">
+      <c r="L16" s="275" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="93" t="inlineStr">
+      <c r="M16" s="276" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="263" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="93" t="n">
+      <c r="C17" s="263" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="93" t="n">
+      <c r="D17" s="263" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="93" t="n">
+      <c r="E17" s="263" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="119" t="inlineStr">
+      <c r="H17" s="264" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="265">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="266">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="121" t="inlineStr">
+      <c r="K17" s="267" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="122" t="inlineStr">
+      <c r="L17" s="277" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="93" t="inlineStr">
+      <c r="M17" s="269" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="270" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="93" t="n">
+      <c r="C18" s="270" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="93" t="n">
+      <c r="D18" s="270" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="93" t="n">
+      <c r="E18" s="270" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="119" t="inlineStr">
+      <c r="H18" s="271" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="199">
+      <c r="I18" s="272">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="200">
+      <c r="J18" s="273">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="121" t="inlineStr">
+      <c r="K18" s="274" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="278" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="93" t="inlineStr">
+      <c r="M18" s="276" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="263" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="93" t="n">
+      <c r="C19" s="263" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="93" t="n">
+      <c r="D19" s="263" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="93" t="n">
+      <c r="E19" s="263" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="123" t="inlineStr">
+      <c r="H19" s="279" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="201">
+      <c r="I19" s="280">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="202">
+      <c r="J19" s="281">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="126" t="inlineStr"/>
-      <c r="L19" s="127" t="inlineStr">
+      <c r="K19" s="282" t="inlineStr"/>
+      <c r="L19" s="283" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="93" t="inlineStr">
+      <c r="M19" s="283" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="270" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="93" t="n">
+      <c r="C20" s="270" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="93" t="n">
+      <c r="D20" s="270" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="93" t="n">
+      <c r="E20" s="270" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="128" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="284" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="128" t="inlineStr">
+      <c r="C22" s="234" t="n"/>
+      <c r="D22" s="234" t="n"/>
+      <c r="E22" s="285" t="n"/>
+      <c r="F22" s="284" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="129" t="inlineStr">
+      <c r="G22" s="234" t="n"/>
+      <c r="H22" s="234" t="n"/>
+      <c r="I22" s="285" t="n"/>
+      <c r="K22" s="286" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="130" t="n"/>
-      <c r="M22" s="130" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="78" t="inlineStr">
+      <c r="L22" s="287" t="n"/>
+      <c r="M22" s="288" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="289" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="93" t="inlineStr">
+      <c r="C23" s="243" t="n"/>
+      <c r="D23" s="243" t="n"/>
+      <c r="E23" s="244" t="n"/>
+      <c r="F23" s="290" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="131" t="inlineStr">
+      <c r="G23" s="243" t="n"/>
+      <c r="H23" s="243" t="n"/>
+      <c r="I23" s="291" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="132" t="inlineStr">
-        <is>
-          <t>AMORTİSMAN VE GERİ DÖNÜŞ</t>
-        </is>
-      </c>
-      <c r="L23" s="130" t="n"/>
-      <c r="M23" s="130" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="79" t="inlineStr">
+      <c r="K23" s="292" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="293" t="n"/>
+      <c r="M23" s="294" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="295" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="93" t="inlineStr">
+      <c r="C24" s="243" t="n"/>
+      <c r="D24" s="243" t="n"/>
+      <c r="E24" s="244" t="n"/>
+      <c r="F24" s="290" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="131" t="inlineStr">
+      <c r="G24" s="243" t="n"/>
+      <c r="H24" s="243" t="n"/>
+      <c r="I24" s="291" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="133" t="inlineStr">
-        <is>
-          <t>Yatırım geri dönüş süresi 4.2 yıl olarak hesaplanmış, şebeke alım garantisi teyit edilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="134" t="inlineStr">
+      <c r="K24" s="296" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="297" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="78" t="inlineStr">
+      <c r="C25" s="243" t="n"/>
+      <c r="D25" s="243" t="n"/>
+      <c r="E25" s="244" t="n"/>
+      <c r="F25" s="268" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="135" t="inlineStr">
+      <c r="G25" s="298" t="n"/>
+      <c r="H25" s="298" t="n"/>
+      <c r="I25" s="298" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="299" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="136" t="inlineStr">
+      <c r="C26" s="243" t="n"/>
+      <c r="D26" s="243" t="n"/>
+      <c r="E26" s="244" t="n"/>
+      <c r="F26" s="300" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -16445,23 +17207,29 @@
       <c r="G26" s="209" t="n"/>
       <c r="H26" s="209" t="n"/>
       <c r="I26" s="210" t="n"/>
-      <c r="K26" s="137" t="inlineStr">
-        <is>
-          <t>FİZİBİLİTE SENARYOSUNU AÇ &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="301" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="302" t="n"/>
+      <c r="C27" s="253" t="n"/>
+      <c r="D27" s="253" t="n"/>
+      <c r="E27" s="254" t="n"/>
       <c r="F27" s="211" t="n"/>
       <c r="G27" s="212" t="n"/>
       <c r="H27" s="212" t="n"/>
       <c r="I27" s="213" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16496,7 +17264,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -16504,7 +17271,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -16549,7 +17315,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -16594,7 +17359,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -16628,7 +17392,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -16662,7 +17425,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
@@ -16687,7 +17449,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
@@ -16770,7 +17531,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -16778,7 +17538,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -16925,7 +17684,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -16933,7 +17691,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -23234,7 +23991,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -23242,7 +23998,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
@@ -23334,7 +24089,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="227" t="inlineStr">
         <is>
@@ -23342,7 +24096,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -24832,7 +25585,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="J44" s="8" t="inlineStr">
         <is>
@@ -24893,7 +25645,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -24901,7 +25652,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -24930,7 +25680,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="69" t="inlineStr">
         <is>
@@ -24945,7 +25694,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="70" t="inlineStr">
         <is>
@@ -24953,7 +25701,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -24966,7 +25713,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -24981,7 +25727,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -25035,7 +25780,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="138" t="inlineStr">
         <is>
@@ -25056,7 +25800,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="141" t="inlineStr">
         <is>
@@ -25469,7 +26212,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="158" t="inlineStr">
         <is>
@@ -25500,54 +26242,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="228" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="160" t="inlineStr">
         <is>
           <t>GES YATIRIM FIZIBILITE SIMÜLATÖRÜ — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="161" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="303" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · GES yatırımcısı, tesis müdürü, CFO, enerji danışmanı</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="162" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="304" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="163" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="305" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -25556,7 +26299,7 @@
       <c r="D6" s="214" t="n"/>
       <c r="E6" s="214" t="n"/>
       <c r="F6" s="215" t="n"/>
-      <c r="H6" s="164" t="inlineStr">
+      <c r="H6" s="306" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -25566,151 +26309,151 @@
       <c r="K6" s="214" t="n"/>
       <c r="L6" s="215" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="101" t="n"/>
-      <c r="C7" s="101" t="n"/>
-      <c r="D7" s="101" t="n"/>
-      <c r="E7" s="101" t="n"/>
-      <c r="F7" s="101" t="n"/>
-      <c r="H7" s="101" t="n"/>
-      <c r="I7" s="101" t="n"/>
-      <c r="J7" s="101" t="n"/>
-      <c r="K7" s="101" t="n"/>
-      <c r="L7" s="101" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="165" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="307" t="n"/>
+      <c r="C7" s="243" t="n"/>
+      <c r="D7" s="243" t="n"/>
+      <c r="E7" s="243" t="n"/>
+      <c r="F7" s="308" t="n"/>
+      <c r="H7" s="309" t="n"/>
+      <c r="I7" s="243" t="n"/>
+      <c r="J7" s="243" t="n"/>
+      <c r="K7" s="243" t="n"/>
+      <c r="L7" s="310" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="311" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="101" t="n"/>
-      <c r="D8" s="101" t="n"/>
-      <c r="E8" s="166" t="inlineStr">
+      <c r="C8" s="243" t="n"/>
+      <c r="D8" s="243" t="n"/>
+      <c r="E8" s="312" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="101" t="n"/>
-      <c r="H8" s="165" t="inlineStr">
+      <c r="F8" s="308" t="n"/>
+      <c r="H8" s="313" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="101" t="n"/>
-      <c r="J8" s="101" t="n"/>
-      <c r="K8" s="167" t="inlineStr">
+      <c r="I8" s="243" t="n"/>
+      <c r="J8" s="243" t="n"/>
+      <c r="K8" s="314" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="101" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="165" t="inlineStr">
+      <c r="L8" s="310" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="311" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="101" t="n"/>
-      <c r="D9" s="101" t="n"/>
-      <c r="E9" s="204">
+      <c r="C9" s="243" t="n"/>
+      <c r="D9" s="243" t="n"/>
+      <c r="E9" s="315">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="101" t="n"/>
-      <c r="H9" s="165" t="inlineStr">
+      <c r="F9" s="308" t="n"/>
+      <c r="H9" s="313" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="101" t="n"/>
-      <c r="J9" s="101" t="n"/>
-      <c r="K9" s="204">
+      <c r="I9" s="243" t="n"/>
+      <c r="J9" s="243" t="n"/>
+      <c r="K9" s="315">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="101" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="165" t="inlineStr">
+      <c r="L9" s="310" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="311" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="101" t="n"/>
-      <c r="D10" s="101" t="n"/>
-      <c r="E10" s="205">
+      <c r="C10" s="243" t="n"/>
+      <c r="D10" s="243" t="n"/>
+      <c r="E10" s="316">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="101" t="n"/>
-      <c r="H10" s="165" t="inlineStr">
+      <c r="F10" s="308" t="n"/>
+      <c r="H10" s="313" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="101" t="n"/>
-      <c r="J10" s="101" t="n"/>
-      <c r="K10" s="205">
+      <c r="I10" s="243" t="n"/>
+      <c r="J10" s="243" t="n"/>
+      <c r="K10" s="316">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="101" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="165" t="inlineStr">
+      <c r="L10" s="310" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="311" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="101" t="n"/>
-      <c r="D11" s="101" t="n"/>
-      <c r="E11" s="206">
+      <c r="C11" s="243" t="n"/>
+      <c r="D11" s="243" t="n"/>
+      <c r="E11" s="317">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="101" t="n"/>
-      <c r="H11" s="165" t="inlineStr">
+      <c r="F11" s="308" t="n"/>
+      <c r="H11" s="313" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="101" t="n"/>
-      <c r="J11" s="101" t="n"/>
-      <c r="K11" s="169" t="inlineStr">
+      <c r="I11" s="243" t="n"/>
+      <c r="J11" s="243" t="n"/>
+      <c r="K11" s="318" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="101" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="101" t="n"/>
-      <c r="C12" s="101" t="n"/>
-      <c r="D12" s="101" t="n"/>
-      <c r="E12" s="101" t="n"/>
-      <c r="F12" s="101" t="n"/>
-      <c r="H12" s="101" t="n"/>
-      <c r="I12" s="101" t="n"/>
-      <c r="J12" s="101" t="n"/>
-      <c r="K12" s="101" t="n"/>
-      <c r="L12" s="101" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="101" t="n"/>
-      <c r="C13" s="101" t="n"/>
-      <c r="D13" s="101" t="n"/>
-      <c r="E13" s="101" t="n"/>
-      <c r="F13" s="101" t="n"/>
-      <c r="H13" s="101" t="n"/>
-      <c r="I13" s="101" t="n"/>
-      <c r="J13" s="101" t="n"/>
-      <c r="K13" s="101" t="n"/>
-      <c r="L13" s="101" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="170" t="inlineStr">
+      <c r="L11" s="310" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="307" t="n"/>
+      <c r="C12" s="243" t="n"/>
+      <c r="D12" s="243" t="n"/>
+      <c r="E12" s="243" t="n"/>
+      <c r="F12" s="308" t="n"/>
+      <c r="H12" s="309" t="n"/>
+      <c r="I12" s="243" t="n"/>
+      <c r="J12" s="243" t="n"/>
+      <c r="K12" s="243" t="n"/>
+      <c r="L12" s="310" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="307" t="n"/>
+      <c r="C13" s="243" t="n"/>
+      <c r="D13" s="243" t="n"/>
+      <c r="E13" s="243" t="n"/>
+      <c r="F13" s="308" t="n"/>
+      <c r="H13" s="309" t="n"/>
+      <c r="I13" s="243" t="n"/>
+      <c r="J13" s="243" t="n"/>
+      <c r="K13" s="243" t="n"/>
+      <c r="L13" s="310" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="319" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -25719,7 +26462,7 @@
       <c r="D14" s="216" t="n"/>
       <c r="E14" s="216" t="n"/>
       <c r="F14" s="217" t="n"/>
-      <c r="H14" s="171" t="inlineStr">
+      <c r="H14" s="320" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -25729,7 +26472,7 @@
       <c r="K14" s="218" t="n"/>
       <c r="L14" s="219" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="220" t="n"/>
       <c r="C15" s="221" t="n"/>
       <c r="D15" s="221" t="n"/>
@@ -25741,70 +26484,185 @@
       <c r="K15" s="224" t="n"/>
       <c r="L15" s="225" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="81" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="321" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="128" t="inlineStr">
+      <c r="C17" s="234" t="n"/>
+      <c r="D17" s="234" t="n"/>
+      <c r="E17" s="234" t="n"/>
+      <c r="F17" s="234" t="n"/>
+      <c r="G17" s="234" t="n"/>
+      <c r="H17" s="234" t="n"/>
+      <c r="I17" s="234" t="n"/>
+      <c r="J17" s="234" t="n"/>
+      <c r="K17" s="234" t="n"/>
+      <c r="L17" s="285" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="322" t="n"/>
+      <c r="C18" s="243" t="n"/>
+      <c r="D18" s="243" t="n"/>
+      <c r="E18" s="243" t="n"/>
+      <c r="F18" s="243" t="n"/>
+      <c r="G18" s="243" t="n"/>
+      <c r="H18" s="243" t="n"/>
+      <c r="I18" s="243" t="n"/>
+      <c r="J18" s="243" t="n"/>
+      <c r="K18" s="243" t="n"/>
+      <c r="L18" s="244" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="323" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="172" t="inlineStr">
+      <c r="C19" s="243" t="n"/>
+      <c r="D19" s="243" t="n"/>
+      <c r="E19" s="243" t="n"/>
+      <c r="F19" s="243" t="n"/>
+      <c r="G19" s="243" t="n"/>
+      <c r="H19" s="243" t="n"/>
+      <c r="I19" s="243" t="n"/>
+      <c r="J19" s="243" t="n"/>
+      <c r="K19" s="243" t="n"/>
+      <c r="L19" s="244" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="324" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="128" t="inlineStr">
+      <c r="C20" s="243" t="n"/>
+      <c r="D20" s="243" t="n"/>
+      <c r="E20" s="243" t="n"/>
+      <c r="F20" s="243" t="n"/>
+      <c r="G20" s="243" t="n"/>
+      <c r="H20" s="243" t="n"/>
+      <c r="I20" s="243" t="n"/>
+      <c r="J20" s="243" t="n"/>
+      <c r="K20" s="243" t="n"/>
+      <c r="L20" s="244" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="323" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="172" t="inlineStr">
+      <c r="C21" s="243" t="n"/>
+      <c r="D21" s="243" t="n"/>
+      <c r="E21" s="243" t="n"/>
+      <c r="F21" s="243" t="n"/>
+      <c r="G21" s="243" t="n"/>
+      <c r="H21" s="243" t="n"/>
+      <c r="I21" s="243" t="n"/>
+      <c r="J21" s="243" t="n"/>
+      <c r="K21" s="243" t="n"/>
+      <c r="L21" s="244" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="324" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="128" t="inlineStr">
+      <c r="C22" s="243" t="n"/>
+      <c r="D22" s="243" t="n"/>
+      <c r="E22" s="243" t="n"/>
+      <c r="F22" s="243" t="n"/>
+      <c r="G22" s="243" t="n"/>
+      <c r="H22" s="243" t="n"/>
+      <c r="I22" s="243" t="n"/>
+      <c r="J22" s="243" t="n"/>
+      <c r="K22" s="243" t="n"/>
+      <c r="L22" s="244" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="323" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="172" t="inlineStr">
+      <c r="C23" s="243" t="n"/>
+      <c r="D23" s="243" t="n"/>
+      <c r="E23" s="243" t="n"/>
+      <c r="F23" s="243" t="n"/>
+      <c r="G23" s="243" t="n"/>
+      <c r="H23" s="243" t="n"/>
+      <c r="I23" s="243" t="n"/>
+      <c r="J23" s="243" t="n"/>
+      <c r="K23" s="243" t="n"/>
+      <c r="L23" s="244" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="324" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="128" t="inlineStr">
+      <c r="C24" s="243" t="n"/>
+      <c r="D24" s="243" t="n"/>
+      <c r="E24" s="243" t="n"/>
+      <c r="F24" s="243" t="n"/>
+      <c r="G24" s="243" t="n"/>
+      <c r="H24" s="243" t="n"/>
+      <c r="I24" s="243" t="n"/>
+      <c r="J24" s="243" t="n"/>
+      <c r="K24" s="243" t="n"/>
+      <c r="L24" s="244" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="323" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="172" t="inlineStr">
+      <c r="C25" s="243" t="n"/>
+      <c r="D25" s="243" t="n"/>
+      <c r="E25" s="243" t="n"/>
+      <c r="F25" s="243" t="n"/>
+      <c r="G25" s="243" t="n"/>
+      <c r="H25" s="243" t="n"/>
+      <c r="I25" s="243" t="n"/>
+      <c r="J25" s="243" t="n"/>
+      <c r="K25" s="243" t="n"/>
+      <c r="L25" s="244" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="324" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="243" t="n"/>
+      <c r="D26" s="243" t="n"/>
+      <c r="E26" s="243" t="n"/>
+      <c r="F26" s="243" t="n"/>
+      <c r="G26" s="243" t="n"/>
+      <c r="H26" s="243" t="n"/>
+      <c r="I26" s="243" t="n"/>
+      <c r="J26" s="243" t="n"/>
+      <c r="K26" s="243" t="n"/>
+      <c r="L26" s="244" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="302" t="n"/>
+      <c r="C27" s="253" t="n"/>
+      <c r="D27" s="253" t="n"/>
+      <c r="E27" s="253" t="n"/>
+      <c r="F27" s="253" t="n"/>
+      <c r="G27" s="253" t="n"/>
+      <c r="H27" s="253" t="n"/>
+      <c r="I27" s="253" t="n"/>
+      <c r="J27" s="253" t="n"/>
+      <c r="K27" s="253" t="n"/>
+      <c r="L27" s="254" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25846,7 +26704,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="179" t="inlineStr">
         <is>
@@ -26341,7 +27198,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
@@ -27088,7 +27944,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="187" t="inlineStr">
         <is>
@@ -27766,7 +28621,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="191" t="inlineStr">
         <is>
@@ -28316,7 +29170,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
